--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_213_R22.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_213_R22.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3641</v>
+        <v>4.6627</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6623</v>
+        <v>5.1289</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2982</v>
+        <v>-0.4663</v>
       </c>
       <c r="G2" t="n">
         <v>2.1817</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3964</v>
+        <v>0.695</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2571</v>
+        <v>0.7237</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1393</v>
+        <v>-0.0288</v>
       </c>
       <c r="V2" t="n">
         <v>0.3943</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5019</v>
+        <v>2.5203</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5244</v>
+        <v>5.1141</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.0225</v>
+        <v>-2.5938</v>
       </c>
       <c r="G3" t="n">
         <v>3.1626</v>
@@ -688,13 +688,13 @@
         <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2517</v>
+        <v>0.2702</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5149</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7665999999999999</v>
+        <v>0.1953</v>
       </c>
       <c r="V3" t="n">
         <v>-1.6083</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. HOARD</t>
+          <t>J. CLARK III</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0167</v>
+        <v>2.3948</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7724</v>
+        <v>2.9138</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2444</v>
+        <v>-0.5191</v>
       </c>
       <c r="G4" t="n">
-        <v>0.474</v>
+        <v>1.9966</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6579</v>
+        <v>-1.9148</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1839</v>
+        <v>3.9114</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5568</v>
+        <v>3.2761</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9446</v>
+        <v>-1.4817</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6122</v>
+        <v>4.7578</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0828</v>
+        <v>-1.2795</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2866</v>
+        <v>-0.4331</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7961</v>
+        <v>-0.8464</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.6237</v>
+        <v>-1.3917</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4705</v>
+        <v>-0.8158</v>
       </c>
       <c r="T4" t="n">
-        <v>0.767</v>
+        <v>-0.1845</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2965</v>
+        <v>-0.6313</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0722</v>
+        <v>1.214</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0722</v>
+        <v>1.214</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. CLARK III</t>
+          <t>J. HOARD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8557</v>
+        <v>1.4784</v>
       </c>
       <c r="E5" t="n">
-        <v>2.442</v>
+        <v>1.5365</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5863</v>
+        <v>-0.0581</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9966</v>
+        <v>0.474</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.9148</v>
+        <v>0.6579</v>
       </c>
       <c r="I5" t="n">
-        <v>3.9114</v>
+        <v>-0.1839</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2761</v>
+        <v>1.5568</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.4817</v>
+        <v>0.9446</v>
       </c>
       <c r="L5" t="n">
-        <v>4.7578</v>
+        <v>0.6122</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2795</v>
+        <v>-1.0828</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4331</v>
+        <v>-0.2866</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8464</v>
+        <v>-0.7961</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.3917</v>
+        <v>-1.6237</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3548</v>
+        <v>-0.0679</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6563</v>
+        <v>0.5311</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6985</v>
+        <v>-0.599</v>
       </c>
       <c r="V5" t="n">
-        <v>1.214</v>
+        <v>1.0722</v>
       </c>
       <c r="W5" t="n">
-        <v>1.214</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W. RAYMAN</t>
+          <t>G. LAVI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1012</v>
+        <v>-0.168</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7221</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8232</v>
+        <v>-0.168</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8199</v>
+        <v>-0.168</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.318</v>
+        <v>-0.168</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5018</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2344</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0504</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.184</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0543</v>
+        <v>-0.168</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3684</v>
+        <v>-0.168</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6859</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2548</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4876</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2328</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. LAVI</t>
+          <t>J. DIBARTOLOMEO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.168</v>
+        <v>-0.3754</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.168</v>
+        <v>-0.9747</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.168</v>
+        <v>-0.7793</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.168</v>
+        <v>-1.3181</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.3318</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-1.4214</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.7532</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.168</v>
+        <v>-1.1111</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.168</v>
+        <v>0.1034</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-1.2144</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.172</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.4995</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.3275</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. DIBARTOLOMEO</t>
+          <t>W. RAYMAN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.981</v>
+        <v>-0.4385</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3634</v>
+        <v>0.2503</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3443</v>
+        <v>-0.6888</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7793</v>
+        <v>-0.8199</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3181</v>
+        <v>-0.318</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5387999999999999</v>
+        <v>-0.5018</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3318</v>
+        <v>0.2344</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.4214</v>
+        <v>0.0504</v>
       </c>
       <c r="L8" t="n">
-        <v>1.7532</v>
+        <v>0.184</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1111</v>
+        <v>-1.0543</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1034</v>
+        <v>-0.3684</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2144</v>
+        <v>-0.6859</v>
       </c>
       <c r="P8" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4336</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2636</v>
+        <v>0.0158</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6972</v>
+        <v>-0.0984</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2032</v>
+        <v>-1.1931</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9315</v>
+        <v>-1.2238</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2717</v>
+        <v>0.0307</v>
       </c>
       <c r="G9" t="n">
         <v>0.1229</v>
@@ -1156,13 +1156,13 @@
         <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7024</v>
+        <v>0.3077</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7468</v>
+        <v>-0.0391</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0444</v>
+        <v>0.3468</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. LUNDBERG</t>
+          <t>M. SANTOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4186</v>
+        <v>-2.13</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3378</v>
+        <v>-1.1948</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0808</v>
+        <v>-0.9352</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0257</v>
+        <v>-0.1112</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3698</v>
+        <v>1.0432</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.656</v>
+        <v>-1.1544</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0833</v>
+        <v>0.9467</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1072</v>
+        <v>1.4655</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1904</v>
+        <v>-0.5188</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.109</v>
+        <v>-1.058</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2626</v>
+        <v>-0.4223</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8464</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9278</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.3917</v>
+        <v>-2.5515</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3195</v>
+        <v>1.6237</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7846</v>
+        <v>-0.4441</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2434</v>
+        <v>-0.0154</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5412</v>
+        <v>-0.4288</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5361</v>
+        <v>-0.6468</v>
       </c>
       <c r="W10" t="n">
-        <v>1.214</v>
+        <v>0.4254</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.7501</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. SANTOS</t>
+          <t>I. LUNDBERG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5003</v>
+        <v>-2.3514</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4307</v>
+        <v>-0.3378</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0697</v>
+        <v>-2.0136</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1112</v>
+        <v>-2.0257</v>
       </c>
       <c r="H11" t="n">
-        <v>1.0432</v>
+        <v>-1.3698</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1544</v>
+        <v>-0.656</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9467</v>
+        <v>0.0833</v>
       </c>
       <c r="K11" t="n">
-        <v>1.4655</v>
+        <v>-0.1072</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5188</v>
+        <v>0.1904</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.058</v>
+        <v>-2.109</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4223</v>
+        <v>-1.2626</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.8464</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9278</v>
+        <v>0.9278</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.5515</v>
+        <v>-1.3917</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6237</v>
+        <v>2.3195</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8145</v>
+        <v>-0.7174</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2513</v>
+        <v>-0.2434</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5632</v>
+        <v>-0.474</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6468</v>
+        <v>-0.5361</v>
       </c>
       <c r="W11" t="n">
-        <v>0.4254</v>
+        <v>1.214</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0722</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2958</v>
+        <v>-3.3294</v>
       </c>
       <c r="E12" t="n">
         <v>0.761</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.0568</v>
+        <v>-4.0904</v>
       </c>
       <c r="G12" t="n">
         <v>-1.0855</v>
@@ -1390,13 +1390,13 @@
         <v>1.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3826</v>
+        <v>0.349</v>
       </c>
       <c r="T12" t="n">
         <v>-0.1019</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4846</v>
+        <v>0.4509</v>
       </c>
       <c r="V12" t="n">
         <v>-3.7527</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.070299999999999</v>
+        <v>1.0704</v>
       </c>
       <c r="E13" t="n">
-        <v>13.5476</v>
+        <v>13.5475</v>
       </c>
       <c r="F13" t="n">
-        <v>-12.4771</v>
+        <v>-12.4773</v>
       </c>
       <c r="G13" t="n">
         <v>2.9482</v>
@@ -1444,7 +1444,7 @@
         <v>17.7269</v>
       </c>
       <c r="K13" t="n">
-        <v>4.2773</v>
+        <v>4.277300000000001</v>
       </c>
       <c r="L13" t="n">
         <v>13.4495</v>
@@ -1468,13 +1468,13 @@
         <v>12.7574</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3339000000000003</v>
+        <v>-0.3339000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>1.2607</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.5945</v>
+        <v>-1.5948</v>
       </c>
       <c r="V13" t="n">
         <v>-3.8634</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.9784</v>
+        <v>5.1249</v>
       </c>
       <c r="E14" t="n">
-        <v>4.9896</v>
+        <v>4.046</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9888</v>
+        <v>1.0788</v>
       </c>
       <c r="G14" t="n">
         <v>3.0154</v>
@@ -1546,13 +1546,13 @@
         <v>0.4639</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3573</v>
+        <v>1.5037</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2255</v>
+        <v>1.2819</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1318</v>
+        <v>0.2219</v>
       </c>
       <c r="V14" t="n">
         <v>0.1418</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8616</v>
+        <v>3.9346</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2937</v>
+        <v>5.1194</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4321</v>
+        <v>-1.1848</v>
       </c>
       <c r="G15" t="n">
         <v>2.2345</v>
@@ -1624,13 +1624,13 @@
         <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1615</v>
+        <v>-0.0885</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1949</v>
+        <v>-0.3692</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0334</v>
+        <v>0.2807</v>
       </c>
       <c r="V15" t="n">
         <v>1.3247</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. BIRUTIS</t>
+          <t>D. SIRVYDIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2684</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6116</v>
+        <v>0.9419</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3432</v>
+        <v>-0.1531</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6427</v>
+        <v>-0.137</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2077</v>
+        <v>0.2378</v>
       </c>
       <c r="I16" t="n">
-        <v>0.435</v>
+        <v>-0.3748</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9717</v>
+        <v>0.6351</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2724</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6993</v>
+        <v>-0.0035</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.329</v>
+        <v>-0.7721</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.4008</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2643</v>
+        <v>-0.3713</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5535</v>
+        <v>-0.002</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7275</v>
+        <v>0.3068</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.174</v>
+        <v>-0.3088</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. WRIGHT</t>
+          <t>L. BIRUTIS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5711000000000001</v>
+        <v>0.7522</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7338</v>
+        <v>1.1398</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1627</v>
+        <v>-0.3876</v>
       </c>
       <c r="G17" t="n">
-        <v>0.029</v>
+        <v>0.6427</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5785</v>
+        <v>0.2077</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.5495</v>
+        <v>0.435</v>
       </c>
       <c r="J17" t="n">
-        <v>3.0238</v>
+        <v>0.9717</v>
       </c>
       <c r="K17" t="n">
-        <v>3.5157</v>
+        <v>0.2724</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.4919</v>
+        <v>0.6993</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.9948</v>
+        <v>-0.329</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9373</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.0576</v>
+        <v>-0.2643</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.3917</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S17" t="n">
-        <v>1.9338</v>
+        <v>0.0373</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1845</v>
+        <v>0.2557</v>
       </c>
       <c r="U17" t="n">
-        <v>2.1183</v>
+        <v>-0.2183</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W17" t="n">
-        <v>1.214</v>
+        <v>1.0722</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.214</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. LO</t>
+          <t>E. ULANOVAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5401</v>
+        <v>0.7419</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4791</v>
+        <v>2.4527</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9389</v>
+        <v>-1.7108</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5760999999999999</v>
+        <v>-0.9431</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.5318</v>
+        <v>-0.6253</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1079</v>
+        <v>-0.3178</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6557</v>
+        <v>1.1547</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.9306</v>
+        <v>-0.6855</v>
       </c>
       <c r="L18" t="n">
-        <v>2.5863</v>
+        <v>1.8402</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0795</v>
+        <v>-2.0978</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6012</v>
+        <v>0.0602</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4783</v>
+        <v>-2.1581</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1959</v>
+        <v>-1.0831</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9831</v>
+        <v>-0.3104</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7872</v>
+        <v>-0.7727000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. SIRVYDIS</t>
+          <t>M. LO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2663</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3522</v>
+        <v>0.8893</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0859</v>
+        <v>-0.3112</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.137</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2378</v>
+        <v>-1.5318</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3748</v>
+        <v>2.1079</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6351</v>
+        <v>1.6557</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6385999999999999</v>
+        <v>-0.9306</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0035</v>
+        <v>2.5863</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7721</v>
+        <v>-1.0795</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4008</v>
+        <v>-0.6012</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3713</v>
+        <v>-0.4783</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9278</v>
+        <v>-0.232</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
         <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5245</v>
+        <v>0.2339</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2829</v>
+        <v>0.3934</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2416</v>
+        <v>-0.1595</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. ULANOVAS</t>
+          <t>M. WRIGHT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1635</v>
+        <v>0.074</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0988</v>
+        <v>2.0876</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9353</v>
+        <v>-2.0136</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9431</v>
+        <v>0.029</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6253</v>
+        <v>2.5785</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3178</v>
+        <v>-2.5495</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1547</v>
+        <v>3.0238</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6855</v>
+        <v>3.5157</v>
       </c>
       <c r="L20" t="n">
-        <v>1.8402</v>
+        <v>-0.4919</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0978</v>
+        <v>-2.9948</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0602</v>
+        <v>-0.9373</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.1581</v>
+        <v>-2.0576</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.6614</v>
+        <v>1.4367</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6642</v>
+        <v>0.1693</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9972</v>
+        <v>1.2674</v>
       </c>
       <c r="V20" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.6083</v>
+        <v>1.214</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.557</v>
+        <v>-1.6242</v>
       </c>
       <c r="E21" t="n">
         <v>-0.981</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5759</v>
+        <v>-0.6432</v>
       </c>
       <c r="G21" t="n">
         <v>-1.5043</v>
@@ -2092,13 +2092,13 @@
         <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2847</v>
+        <v>-0.3519</v>
       </c>
       <c r="T21" t="n">
         <v>-0.2987</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0141</v>
+        <v>-0.0532</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0554</v>
+        <v>-1.803</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0483</v>
+        <v>1.1663</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.1037</v>
+        <v>-2.9693</v>
       </c>
       <c r="G22" t="n">
         <v>-2.4753</v>
@@ -2170,13 +2170,13 @@
         <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7398</v>
+        <v>-0.4874</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5149</v>
+        <v>-0.3969</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2249</v>
+        <v>-0.0905</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1127</v>
+        <v>-2.4456</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0736</v>
+        <v>-1.1915</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0391</v>
+        <v>-1.2541</v>
       </c>
       <c r="G23" t="n">
         <v>0.5447</v>
@@ -2248,13 +2248,13 @@
         <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3374</v>
+        <v>1.0045</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9085</v>
+        <v>0.7905</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5711000000000001</v>
+        <v>0.2139</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2836</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.9947</v>
+        <v>-5.6193</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0752</v>
+        <v>-3.1932</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.9194</v>
+        <v>-2.4261</v>
       </c>
       <c r="G24" t="n">
         <v>-4.9308</v>
@@ -2326,13 +2326,13 @@
         <v>1.3917</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6721</v>
+        <v>-0.2967</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1098</v>
+        <v>-0.2278</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5623</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>0.5361</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.070399999999999</v>
+        <v>0.5023999999999988</v>
       </c>
       <c r="E25" t="n">
         <v>12.4773</v>
       </c>
       <c r="F25" t="n">
-        <v>-13.5474</v>
+        <v>-11.975</v>
       </c>
       <c r="G25" t="n">
         <v>-2.948099999999999</v>
@@ -2395,7 +2395,7 @@
         <v>-13.4496</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.319399999999999</v>
+        <v>-2.3194</v>
       </c>
       <c r="Q25" t="n">
         <v>-12.7574</v>
@@ -2404,19 +2404,19 @@
         <v>10.438</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3338999999999993</v>
+        <v>1.9065</v>
       </c>
       <c r="T25" t="n">
-        <v>1.5947</v>
+        <v>1.5946</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.2607</v>
+        <v>0.3119000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>3.8634</v>
       </c>
       <c r="W25" t="n">
-        <v>8.8612</v>
+        <v>8.861200000000002</v>
       </c>
       <c r="X25" t="n">
         <v>-4.997800000000001</v>
